--- a/bioinfo_revision/supplementary_tables/TableS1_Aggregated_confusion_matrices_MRGN_MRPC.xlsx
+++ b/bioinfo_revision/supplementary_tables/TableS1_Aggregated_confusion_matrices_MRGN_MRPC.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/audreyq.fu/Documents/CausalNet/Data/MRGN_simulation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/audreyq.fu/Documents/CausalNet/Reports/MRGNtrio/supplementary_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5708BC5B-C6CA-EB4A-9D0E-B309B7F7CB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5E2D87-EA68-9A4E-BAB2-77BC92ED5409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="1960" windowWidth="26840" windowHeight="15160" xr2:uid="{CDEEC52E-3057-974F-98CC-285FC7A2BDAD}"/>
+    <workbookView xWindow="5160" yWindow="1960" windowWidth="26840" windowHeight="15160" activeTab="1" xr2:uid="{CDEEC52E-3057-974F-98CC-285FC7A2BDAD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MRGN-CSq" sheetId="1" r:id="rId1"/>
+    <sheet name="MRPC-CSq" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
   <si>
     <t>Inferred \ True</t>
   </si>
@@ -72,6 +73,9 @@
   </si>
   <si>
     <t>Recall</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
@@ -693,4 +697,274 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AF24AF-EF06-2A4F-BB6B-A0CAEDFB5AB5}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>90</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>162</v>
+      </c>
+      <c r="H2">
+        <v>0.55600000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>51</v>
+      </c>
+      <c r="G3">
+        <v>95</v>
+      </c>
+      <c r="H3">
+        <v>0.38900000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1">
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>74</v>
+      </c>
+      <c r="H4">
+        <v>0.59499999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>69</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>78</v>
+      </c>
+      <c r="H5">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>39</v>
+      </c>
+      <c r="H6">
+        <v>0.61499999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>101</v>
+      </c>
+      <c r="D7">
+        <v>104</v>
+      </c>
+      <c r="E7">
+        <v>82</v>
+      </c>
+      <c r="F7">
+        <v>75</v>
+      </c>
+      <c r="G7">
+        <v>452</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>180</v>
+      </c>
+      <c r="C9">
+        <v>180</v>
+      </c>
+      <c r="D9">
+        <v>180</v>
+      </c>
+      <c r="E9">
+        <v>180</v>
+      </c>
+      <c r="F9">
+        <v>180</v>
+      </c>
+      <c r="G9">
+        <v>900</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.29299999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>